--- a/portfolio_bbc.xlsx
+++ b/portfolio_bbc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\examb\OneDrive\바탕 화면\Naver MYBOX\Others\AI_WORKS\web_portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C8EDCFC-03D8-4838-88A9-D6433BFECB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CEBF08-BF0C-474F-8807-8441954A0C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,10 +64,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>티씨케이</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>삼양식품</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -140,10 +136,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>064760</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>003230</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -201,6 +193,14 @@
   </si>
   <si>
     <t>2209</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>케이엔제이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>272110</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -250,7 +250,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -344,6 +344,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -351,7 +373,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -387,6 +409,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -727,7 +758,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
@@ -744,7 +775,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
@@ -752,50 +783,50 @@
         <v>9</v>
       </c>
       <c r="B4" s="6">
-        <v>122200</v>
+        <v>601000</v>
       </c>
       <c r="C4" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6">
-        <v>601000</v>
+      <c r="B5" s="5">
+        <v>5.97</v>
       </c>
       <c r="C5" s="7">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="5">
-        <v>5.97</v>
+      <c r="B6" s="6">
+        <v>19360</v>
       </c>
       <c r="C6" s="7">
-        <v>1000</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
@@ -803,50 +834,50 @@
         <v>12</v>
       </c>
       <c r="B7" s="6">
-        <v>19360</v>
+        <v>2965</v>
       </c>
       <c r="C7" s="7">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="6">
-        <v>2965</v>
+      <c r="B8" s="7">
+        <v>22950</v>
       </c>
       <c r="C8" s="7">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="7">
-        <v>22950</v>
+      <c r="B9" s="8">
+        <v>208.74</v>
       </c>
       <c r="C9" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
@@ -854,33 +885,33 @@
         <v>15</v>
       </c>
       <c r="B10" s="8">
-        <v>208.74</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="C10" s="7">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="8">
-        <v>16.850000000000001</v>
+      <c r="B11" s="6">
+        <v>39200</v>
       </c>
       <c r="C11" s="7">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
@@ -888,16 +919,16 @@
         <v>17</v>
       </c>
       <c r="B12" s="6">
-        <v>39200</v>
+        <v>453000</v>
       </c>
       <c r="C12" s="7">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
@@ -905,16 +936,16 @@
         <v>18</v>
       </c>
       <c r="B13" s="6">
-        <v>453000</v>
+        <v>270000</v>
       </c>
       <c r="C13" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
@@ -922,16 +953,16 @@
         <v>19</v>
       </c>
       <c r="B14" s="6">
-        <v>270000</v>
+        <v>99300</v>
       </c>
       <c r="C14" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
@@ -939,44 +970,44 @@
         <v>20</v>
       </c>
       <c r="B15" s="6">
-        <v>99300</v>
+        <v>98603</v>
       </c>
       <c r="C15" s="7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B16" s="6">
-        <v>98603</v>
+        <v>584000</v>
       </c>
       <c r="C16" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B17" s="6">
-        <v>584000</v>
+        <v>14840</v>
       </c>
       <c r="C17" s="7">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -985,38 +1016,38 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="6">
-        <v>14840</v>
-      </c>
-      <c r="C18" s="7">
-        <v>35</v>
+      <c r="B18" s="9">
+        <v>16601</v>
+      </c>
+      <c r="C18" s="11">
+        <v>40</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="9">
-        <v>16601</v>
-      </c>
-      <c r="C19" s="11">
-        <v>40</v>
+      <c r="B19" s="15">
+        <v>38202</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio_bbc.xlsx
+++ b/portfolio_bbc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\examb\OneDrive\바탕 화면\Naver MYBOX\Others\AI_WORKS\web_portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CEBF08-BF0C-474F-8807-8441954A0C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADFB210-C382-49C0-B0B0-8987D685A4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>종목명</t>
   </si>
@@ -88,10 +88,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>USAR</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>S-OIL우</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -153,10 +149,6 @@
   </si>
   <si>
     <t>COIN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>USAR</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -409,7 +401,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
@@ -721,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="5" max="5" width="8.796875" style="12"/>
@@ -758,7 +750,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
@@ -775,7 +767,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
@@ -792,7 +784,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
@@ -806,10 +798,10 @@
         <v>1000</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
@@ -826,7 +818,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
@@ -843,7 +835,7 @@
         <v>5</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
@@ -860,7 +852,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
@@ -877,24 +869,24 @@
         <v>6</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="8">
-        <v>16.850000000000001</v>
+      <c r="B10" s="6">
+        <v>39200</v>
       </c>
       <c r="C10" s="7">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
@@ -902,16 +894,16 @@
         <v>16</v>
       </c>
       <c r="B11" s="6">
-        <v>39200</v>
+        <v>453000</v>
       </c>
       <c r="C11" s="7">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
@@ -919,16 +911,16 @@
         <v>17</v>
       </c>
       <c r="B12" s="6">
-        <v>453000</v>
+        <v>270000</v>
       </c>
       <c r="C12" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
@@ -936,16 +928,16 @@
         <v>18</v>
       </c>
       <c r="B13" s="6">
-        <v>270000</v>
+        <v>99300</v>
       </c>
       <c r="C13" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
@@ -953,44 +945,44 @@
         <v>19</v>
       </c>
       <c r="B14" s="6">
-        <v>99300</v>
+        <v>98603</v>
       </c>
       <c r="C14" s="7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B15" s="6">
-        <v>98603</v>
+        <v>584000</v>
       </c>
       <c r="C15" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B16" s="6">
-        <v>584000</v>
+        <v>14840</v>
       </c>
       <c r="C16" s="7">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -999,55 +991,38 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="6">
-        <v>14840</v>
-      </c>
-      <c r="C17" s="7">
-        <v>35</v>
+      <c r="B17" s="9">
+        <v>16601</v>
+      </c>
+      <c r="C17" s="11">
+        <v>40</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" s="13" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="9">
-        <v>16601</v>
-      </c>
-      <c r="C18" s="11">
-        <v>40</v>
+      <c r="B18" s="15">
+        <v>38202</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A19" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="15">
-        <v>38202</v>
-      </c>
-      <c r="C19" s="14">
-        <v>20</v>
-      </c>
-      <c r="D19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
